--- a/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,18 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +52,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00366092"/>
         <bgColor rgb="00366092"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,11 +79,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyFont="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,9 +527,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Ключевая ставка Банка России, % годовых</t>
+        </is>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Ключевая ставка Банка России на дату расчёта — cbr.ru, раздел „Ключевая ставка“</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -527,7 +558,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7">
-        <f>B7*0.15/365*D9</f>
+        <f>B7*B5/365*D9</f>
         <v/>
       </c>
       <c r="D7">

--- a/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Калькулятор убытков" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Калькулятор убытков" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +40,16 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <color rgb="000000FF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +66,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
         <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,18 +92,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyFont="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,8 +512,6 @@
           <t>Сумма по КС-2</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2">
         <f>B2</f>
         <v/>
@@ -506,8 +523,6 @@
           <t>Фактически оплачено</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3">
         <f>B3</f>
         <v/>
@@ -519,8 +534,6 @@
           <t>Удержано</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4">
         <f>B4</f>
         <v/>
@@ -532,13 +545,12 @@
           <t>Ключевая ставка Банка России, % годовых</t>
         </is>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Ключевая ставка Банка России на дату расчёта — cbr.ru, раздел „Ключевая ставка“</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Ключевая ставка Банка России на дату расчёта — cbr.ru, раздел «Ключевая ставка». Вводите годовой процент числом: например, 16 — не 0,16</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -546,9 +558,6 @@
           <t>УБЫТКИ:</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -556,9 +565,8 @@
           <t>Проценты по ст. 395 ГК РФ</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7">
-        <f>B7*B5/365*D9</f>
+        <f>IF($B$5="","",B7*$B$5/100/365*D9)</f>
         <v/>
       </c>
       <c r="D7">
@@ -572,7 +580,6 @@
           <t>Неустойка по договору (%/день)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8">
         <f>B8*D9</f>
         <v/>
@@ -588,27 +595,18 @@
           <t>Дни просрочки</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9">
-        <f>ЕСЛИ(И(B2&lt;&gt;"";B3&lt;&gt;"");B9;0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-    </row>
+        <f>IF(AND(B2&lt;&gt;"",B3&lt;&gt;""),B9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>ИТОГО к взысканию:</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
       <c r="D11">
         <f>D2-D3+C7+C8</f>
         <v/>

--- a/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Калькулятор убытков" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Калькулятор убытков" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,26 +30,8 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="000000FF"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -60,17 +42,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00366092"/>
         <bgColor rgb="00366092"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,23 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,6 +470,8 @@
           <t>Сумма по КС-2</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2">
         <f>B2</f>
         <v/>
@@ -523,6 +483,8 @@
           <t>Фактически оплачено</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3">
         <f>B3</f>
         <v/>
@@ -534,23 +496,18 @@
           <t>Удержано</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4">
         <f>B4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Ключевая ставка Банка России, % годовых</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Ключевая ставка Банка России на дату расчёта — cbr.ru, раздел «Ключевая ставка». Вводите годовой процент числом: например, 16 — не 0,16</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -558,6 +515,9 @@
           <t>УБЫТКИ:</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -565,8 +525,9 @@
           <t>Проценты по ст. 395 ГК РФ</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7">
-        <f>IF($B$5="","",B7*$B$5/100/365*D9)</f>
+        <f>B7*0.15/365*D9</f>
         <v/>
       </c>
       <c r="D7">
@@ -580,6 +541,7 @@
           <t>Неустойка по договору (%/день)</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8">
         <f>B8*D9</f>
         <v/>
@@ -595,18 +557,27 @@
           <t>Дни просрочки</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9">
-        <f>IF(AND(B2&lt;&gt;"",B3&lt;&gt;""),B9,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10"/>
+        <f>ЕСЛИ(И(B2&lt;&gt;"";B3&lt;&gt;"");B9;0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>ИТОГО к взысканию:</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11">
         <f>D2-D3+C7+C8</f>
         <v/>

--- a/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
+++ b/products-storage/07-uderzhaniya-shtrafy-zachety/04-raschet-ubytkov.xlsx
@@ -504,7 +504,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ключевая ставка Банка России, % (на периоды просрочки)</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -527,7 +531,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7">
-        <f>B7*0.15/365*D9</f>
+        <f>B7*B5/100/365*B9</f>
         <v/>
       </c>
       <c r="D7">
@@ -543,7 +547,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8">
-        <f>B8*D9</f>
+        <f>B8*B9</f>
         <v/>
       </c>
       <c r="D8">
@@ -559,10 +563,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
-      <c r="D9">
-        <f>ЕСЛИ(И(B2&lt;&gt;"";B3&lt;&gt;"");B9;0)</f>
-        <v/>
-      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
